--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$100</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 11.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 14.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2588000</v>
+        <v>2582000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2588000</v>
+        <v>2582000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5176000</v>
+        <v>5164000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5176000</v>
+        <v>5164000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1863360</v>
+        <v>1859040</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1863360</v>
+        <v>1859040</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>455488</v>
+        <v>454432</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>455488</v>
+        <v>454432</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8648578.4</v>
+        <v>8628527.6</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8648578.4</v>
+        <v>8628527.6</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4073512</v>
+        <v>4064068</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4073512</v>
+        <v>4064068</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4954726</v>
+        <v>4943239</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4954726</v>
+        <v>4943239</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>754402</v>
+        <v>752653</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>754402</v>
+        <v>752653</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>559784.4</v>
+        <v>558486.6</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>559784.4</v>
+        <v>558486.6</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3703,31 +3703,31 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B70" s="9" t="n">
-        <v>7414</v>
+        <v>5870</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>Carport Airport Munich</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>94000</v>
+        <v>903700</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>94000</v>
+        <v>903700</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3743,35 +3743,39 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="K70" s="12" t="inlineStr"/>
+      <c r="K70" s="12" t="inlineStr">
+        <is>
+          <t>€17 500</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
         <v>46255</v>
       </c>
       <c r="B71" s="9" t="n">
-        <v>7894</v>
+        <v>7414</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F71" s="10" t="n">
-        <v>185968</v>
+        <v>94000</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>185968</v>
+        <v>94000</v>
       </c>
       <c r="H71" s="11">
         <f>F71-G71</f>
@@ -3808,14 +3812,14 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F72" s="10" t="n">
-        <v>185967.99</v>
+        <v>185968</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>185967.99</v>
+        <v>185968</v>
       </c>
       <c r="H72" s="11">
         <f>F72-G72</f>
@@ -3852,14 +3856,14 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F73" s="10" t="n">
-        <v>737597.4</v>
+        <v>185967.99</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>737597.4</v>
+        <v>185967.99</v>
       </c>
       <c r="H73" s="11">
         <f>F73-G73</f>
@@ -3882,11 +3886,11 @@
         <v>46255</v>
       </c>
       <c r="B74" s="9" t="n">
-        <v>8898</v>
+        <v>7894</v>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
@@ -3896,14 +3900,14 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F74" s="10" t="n">
-        <v>188043.75</v>
+        <v>737597.4</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>188043.75</v>
+        <v>737597.4</v>
       </c>
       <c r="H74" s="11">
         <f>F74-G74</f>
@@ -3923,19 +3927,19 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>46260</v>
+        <v>46255</v>
       </c>
       <c r="B75" s="9" t="n">
-        <v>6406</v>
+        <v>8898</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -3944,10 +3948,10 @@
         </is>
       </c>
       <c r="F75" s="10" t="n">
-        <v>218602</v>
+        <v>188043.75</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>170788</v>
+        <v>188043.75</v>
       </c>
       <c r="H75" s="11">
         <f>F75-G75</f>
@@ -3955,7 +3959,7 @@
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3967,31 +3971,31 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B76" s="9" t="n">
-        <v>8878</v>
+        <v>6406</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F76" s="10" t="n">
-        <v>12823</v>
+        <v>218602</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>12823</v>
+        <v>170788</v>
       </c>
       <c r="H76" s="11">
         <f>F76-G76</f>
@@ -3999,7 +4003,7 @@
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4011,31 +4015,31 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="B77" s="9" t="n">
-        <v>6356</v>
+        <v>8878</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>А ТОВ КОМПАНІЯ ВОЛЬТ СЕРВІС ГРУП</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>2818642.56</v>
+        <v>12823</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>2818642.56</v>
+        <v>12823</v>
       </c>
       <c r="H77" s="11">
         <f>F77-G77</f>
@@ -4048,42 +4052,38 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="K77" s="12" t="inlineStr">
-        <is>
-          <t>€54 456</t>
-        </is>
-      </c>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K77" s="12" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
         <v>46268</v>
       </c>
       <c r="B78" s="9" t="n">
-        <v>7414</v>
+        <v>6356</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>13349.1</v>
+        <v>2812107.84</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>13349.1</v>
+        <v>2812107.84</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4099,35 +4099,39 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K78" s="12" t="inlineStr"/>
+      <c r="K78" s="12" t="inlineStr">
+        <is>
+          <t>€54 456</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="B79" s="9" t="n">
-        <v>8497</v>
+        <v>7414</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F79" s="10" t="n">
-        <v>1564446</v>
+        <v>13349.1</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>1564446</v>
+        <v>13349.1</v>
       </c>
       <c r="H79" s="11">
         <f>F79-G79</f>
@@ -4143,39 +4147,35 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K79" s="12" t="inlineStr">
-        <is>
-          <t>€30 225</t>
-        </is>
-      </c>
+      <c r="K79" s="12" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46278</v>
+        <v>46272</v>
       </c>
       <c r="B80" s="9" t="n">
-        <v>5870</v>
+        <v>8497</v>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Carport Airport Munich</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>905800</v>
+        <v>1560819</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>0</v>
+        <v>1560819</v>
       </c>
       <c r="H80" s="11">
         <f>F80-G80</f>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="K80" s="12" t="inlineStr">
         <is>
-          <t>€17 500</t>
+          <t>€30 225</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4440,10 +4440,10 @@
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>17297208.56</v>
+        <v>17257106.84</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>7214360.56</v>
+        <v>7197634.84</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>2882721.44</v>
+        <v>2876038.16</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>457713.68</v>
+        <v>456652.52</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>521482</v>
+        <v>520273</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3325062.4</v>
+        <v>3317353.6</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>665012.48</v>
+        <v>663470.72</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
@@ -5360,7 +5360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5411,26 +5411,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46260</v>
+        <v>46279</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>6406</v>
+        <v>7002</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>218602</v>
+        <v>573945</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -5438,26 +5438,82 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>7002</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Фора SCP Млиново</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Шостий платіж (Допка)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>257000</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11">
+        <f>E3-F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>170788</v>
+      </c>
+      <c r="G4" s="11">
+        <f>E4-F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E3" s="13">
-        <f>SUM(E2:E2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="13">
-        <f>SUM(F2:F2)</f>
-        <v/>
-      </c>
-      <c r="G3" s="13">
-        <f>SUM(G2:G2)</f>
+      <c r="E5" s="13">
+        <f>SUM(E2:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="13">
+        <f>SUM(F2:F4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="13">
+        <f>SUM(G2:G4)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 14.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 15.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2582000</v>
+        <v>2576000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2582000</v>
+        <v>2576000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5164000</v>
+        <v>5152000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5164000</v>
+        <v>5152000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1859040</v>
+        <v>1854720</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1859040</v>
+        <v>1854720</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>454432</v>
+        <v>453376</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>454432</v>
+        <v>453376</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8628527.6</v>
+        <v>8608476.800000001</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8628527.6</v>
+        <v>8608476.800000001</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4064068</v>
+        <v>4054624</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4064068</v>
+        <v>4054624</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4943239</v>
+        <v>4931752</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4943239</v>
+        <v>4931752</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>752653</v>
+        <v>750904</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>752653</v>
+        <v>750904</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>558486.6</v>
+        <v>557188.8</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>558486.6</v>
+        <v>557188.8</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>903700</v>
+        <v>901600</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>903700</v>
+        <v>901600</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2812107.84</v>
+        <v>2805573.12</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>2812107.84</v>
+        <v>2805573.12</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1560819</v>
+        <v>1557192</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>1560819</v>
+        <v>1557192</v>
       </c>
       <c r="H80" s="11">
         <f>F80-G80</f>
@@ -4287,7 +4287,7 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B83" s="9" t="n">
         <v>8898</v>
@@ -4334,16 +4334,16 @@
         <v>46283</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>3456</v>
+        <v>7508</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>А Підселання фундаменту</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>335974.68</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4375,31 +4375,31 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>7508</v>
+        <v>5910</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>17217005.12</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>0</v>
+        <v>7180909.12</v>
       </c>
       <c r="H85" s="11">
         <f>F85-G85</f>
@@ -4415,7 +4415,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K85" s="12" t="inlineStr"/>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
@@ -4436,14 +4440,14 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>17257106.84</v>
+        <v>2869354.88</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>7197634.84</v>
+        <v>455591.36</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>€334 181</t>
+          <t>€55 694</t>
         </is>
       </c>
     </row>
@@ -4470,16 +4474,16 @@
         <v>46286</v>
       </c>
       <c r="B87" s="9" t="n">
-        <v>5910</v>
+        <v>7414</v>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
@@ -4488,10 +4492,10 @@
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>2876038.16</v>
+        <v>44148.4</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>456652.52</v>
+        <v>0</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4507,27 +4511,23 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K87" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K87" s="12" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>7414</v>
+        <v>6352</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>44148.4</v>
+        <v>1119237.26</v>
       </c>
       <c r="G88" s="10" t="n">
         <v>0</v>
@@ -4576,11 +4576,11 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>1119237.26</v>
+        <v>371982.96</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>
@@ -4603,28 +4603,28 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>6352</v>
+        <v>7244</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>371982.96</v>
+        <v>132708.6</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4650,11 +4650,11 @@
         <v>46295</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>7244</v>
+        <v>7414</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -4664,11 +4664,11 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>132708.6</v>
+        <v>57497.5</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4691,14 +4691,14 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>7414</v>
+        <v>4766</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
@@ -4708,11 +4708,11 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>57497.5</v>
+        <v>1263447.42</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4728,21 +4728,21 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K92" s="12" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>4766</v>
+        <v>6024</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>1263447.42</v>
+        <v>246402</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4796,11 +4796,11 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>246402</v>
+        <v>3999</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -4823,28 +4823,28 @@
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>6024</v>
+        <v>8497</v>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>3999</v>
+        <v>519064.0000000001</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -4863,23 +4863,27 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K95" s="12" t="inlineStr"/>
+      <c r="K95" s="12" t="inlineStr">
+        <is>
+          <t>€10 075</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B96" s="9" t="n">
-        <v>8497</v>
+        <v>6356</v>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
@@ -4888,7 +4892,7 @@
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>520273</v>
+        <v>3309644.8</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -4909,13 +4913,13 @@
       </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
-          <t>€10 075</t>
+          <t>€64 240</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="B97" s="9" t="n">
         <v>7894</v>
@@ -4959,28 +4963,28 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="B98" s="9" t="n">
-        <v>6356</v>
+        <v>6352</v>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3317353.6</v>
+        <v>651792.28</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -4999,36 +5003,32 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K98" s="12" t="inlineStr">
-        <is>
-          <t>€64 240</t>
-        </is>
-      </c>
+      <c r="K98" s="12" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B99" s="9" t="n">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>651792.28</v>
+        <v>661928.9600000001</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
@@ -5047,77 +5047,33 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K99" s="12" t="inlineStr"/>
+      <c r="K99" s="12" t="inlineStr">
+        <is>
+          <t>€12 848</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B100" s="9" t="n">
-        <v>6356</v>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>Хома</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="F100" s="10" t="n">
-        <v>663470.72</v>
-      </c>
-      <c r="G100" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="11">
-        <f>F100-G100</f>
-        <v/>
-      </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>очікується</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="K100" s="12" t="inlineStr">
-        <is>
-          <t>€12 848</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="E101" s="3" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F101" s="13">
-        <f>SUM(F2:F100)</f>
-        <v/>
-      </c>
-      <c r="G101" s="13">
-        <f>SUM(G2:G100)</f>
-        <v/>
-      </c>
-      <c r="H101" s="13">
-        <f>SUM(H2:H100)</f>
+      <c r="F100" s="13">
+        <f>SUM(F2:F99)</f>
+        <v/>
+      </c>
+      <c r="G100" s="13">
+        <f>SUM(G2:G99)</f>
+        <v/>
+      </c>
+      <c r="H100" s="13">
+        <f>SUM(H2:H99)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I100"/>
+  <autoFilter ref="A1:I99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$99</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 15.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 16.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2576000</v>
+        <v>2575500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2576000</v>
+        <v>2575500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5152000</v>
+        <v>5151000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5152000</v>
+        <v>5151000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1854720</v>
+        <v>1854360</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1854720</v>
+        <v>1854360</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>453376</v>
+        <v>453288</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>453376</v>
+        <v>453288</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8608476.800000001</v>
+        <v>8606805.9</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8608476.800000001</v>
+        <v>8606805.9</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4054624</v>
+        <v>4053837</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4054624</v>
+        <v>4053837</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4931752</v>
+        <v>4930794.75</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4931752</v>
+        <v>4930794.75</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>750904</v>
+        <v>750758.25</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>750904</v>
+        <v>750758.25</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>557188.8</v>
+        <v>557080.65</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>557188.8</v>
+        <v>557080.65</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>901600</v>
+        <v>901425</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>901600</v>
+        <v>901425</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2805573.12</v>
+        <v>2805028.56</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>2805573.12</v>
+        <v>2805028.56</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1557192</v>
+        <v>1556889.75</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>1557192</v>
+        <v>1556889.75</v>
       </c>
       <c r="H80" s="11">
         <f>F80-G80</f>
@@ -4199,14 +4199,14 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>7002</v>
+        <v>8898</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -4216,11 +4216,11 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>573945</v>
+        <v>188043.75</v>
       </c>
       <c r="G81" s="10" t="n">
         <v>0</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B82" s="9" t="n">
         <v>7002</v>
@@ -4260,11 +4260,11 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>257000</v>
+        <v>573945</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4287,14 +4287,14 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>8898</v>
+        <v>7002</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -4304,11 +4304,11 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>188043.75</v>
+        <v>257000</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>17217005.12</v>
+        <v>17213663.31</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>7180909.12</v>
+        <v>7179515.31</v>
       </c>
       <c r="H85" s="11">
         <f>F85-G85</f>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>2869354.88</v>
+        <v>2868797.94</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>455591.36</v>
+        <v>455502.93</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>519064.0000000001</v>
+        <v>518963.25</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>3309644.8</v>
+        <v>3309002.4</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>661928.9600000001</v>
+        <v>661800.48</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5367,23 +5367,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>7002</v>
+        <v>8898</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>573945</v>
+        <v>188043.75</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5395,26 +5395,26 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46279</v>
+        <v>46260</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>7002</v>
+        <v>6406</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>257000</v>
+        <v>218602</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -5422,54 +5422,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>6406</v>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Максим Яловий Чинадієво</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>218602</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>170788</v>
-      </c>
-      <c r="G4" s="11">
-        <f>E4-F4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E5" s="13">
-        <f>SUM(E2:E4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>SUM(F2:F4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>SUM(G2:G4)</f>
+      <c r="E4" s="13">
+        <f>SUM(E2:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="13">
+        <f>SUM(F2:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="13">
+        <f>SUM(G2:G3)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5054,26 +5054,70 @@
       </c>
     </row>
     <row r="100">
-      <c r="E100" s="3" t="inlineStr">
+      <c r="A100" s="8" t="n">
+        <v>46343</v>
+      </c>
+      <c r="B100" s="9" t="n">
+        <v>8238</v>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>Іщук</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>550000</v>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="11">
+        <f>F100-G100</f>
+        <v/>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F100" s="13">
-        <f>SUM(F2:F99)</f>
-        <v/>
-      </c>
-      <c r="G100" s="13">
-        <f>SUM(G2:G99)</f>
-        <v/>
-      </c>
-      <c r="H100" s="13">
-        <f>SUM(H2:H99)</f>
+      <c r="F101" s="13">
+        <f>SUM(F2:F100)</f>
+        <v/>
+      </c>
+      <c r="G101" s="13">
+        <f>SUM(G2:G100)</f>
+        <v/>
+      </c>
+      <c r="H101" s="13">
+        <f>SUM(H2:H100)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I99"/>
+  <autoFilter ref="A1:I100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5084,7 +5128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5283,25 +5327,48 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>лис 2026</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>SUMIF('Графік надходжень'!J:J,"2026-11",'Графік надходжень'!F:F)</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>SUMIF('Графік надходжень'!J:J,"2026-11",'Графік надходжень'!G:G)</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="14">
+        <f>IF(B9=0,0,C9/B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="B9" s="13">
-        <f>SUM(B2:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="13">
-        <f>SUM(C2:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="13">
-        <f>SUM(D2:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="15">
-        <f>IF(B9=0,0,C9/B9)</f>
+      <c r="B10" s="13">
+        <f>SUM(B2:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="13">
+        <f>SUM(C2:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="13">
+        <f>SUM(D2:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>IF(B10=0,0,C10/B10)</f>
         <v/>
       </c>
     </row>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 16.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 17.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2575500</v>
+        <v>2572500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2575500</v>
+        <v>2572500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5151000</v>
+        <v>5145000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5151000</v>
+        <v>5145000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1854360</v>
+        <v>1852200</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1854360</v>
+        <v>1852200</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>453288</v>
+        <v>452760</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>453288</v>
+        <v>452760</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8606805.9</v>
+        <v>8596780.5</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8606805.9</v>
+        <v>8596780.5</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4053837</v>
+        <v>4049115</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4053837</v>
+        <v>4049115</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4930794.75</v>
+        <v>4925051.25</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4930794.75</v>
+        <v>4925051.25</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>750758.25</v>
+        <v>749883.75</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>750758.25</v>
+        <v>749883.75</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>557080.65</v>
+        <v>556431.75</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>557080.65</v>
+        <v>556431.75</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>901425</v>
+        <v>900375</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>901425</v>
+        <v>900375</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2805028.56</v>
+        <v>2801761.2</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>2805028.56</v>
+        <v>2801761.2</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1556889.75</v>
+        <v>1555076.25</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>1556889.75</v>
+        <v>1555076.25</v>
       </c>
       <c r="H80" s="11">
         <f>F80-G80</f>
@@ -4199,14 +4199,14 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="B81" s="9" t="n">
-        <v>8898</v>
+        <v>8304</v>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>-26 ГШ Фундамент домобудування Валерій Гибаленко</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
@@ -4216,14 +4216,14 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F81" s="10" t="n">
-        <v>188043.75</v>
+        <v>117310</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>0</v>
+        <v>117310</v>
       </c>
       <c r="H81" s="11">
         <f>F81-G81</f>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4243,14 +4243,14 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>7002</v>
+        <v>8898</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -4260,11 +4260,11 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>573945</v>
+        <v>188043.75</v>
       </c>
       <c r="G82" s="10" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4304,11 +4304,11 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>257000</v>
+        <v>573945</v>
       </c>
       <c r="G83" s="10" t="n">
         <v>0</v>
@@ -4334,25 +4334,25 @@
         <v>46283</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>7508</v>
+        <v>7002</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>257000</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4375,31 +4375,31 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>5910</v>
+        <v>7508</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>17213663.31</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>7179515.31</v>
+        <v>0</v>
       </c>
       <c r="H85" s="11">
         <f>F85-G85</f>
@@ -4415,11 +4415,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K85" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K85" s="12" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
@@ -4440,14 +4436,14 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>2868797.94</v>
+        <v>17193612.45</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>455502.93</v>
+        <v>7171152.45</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4465,7 +4461,7 @@
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>€55 694</t>
+          <t>€334 181</t>
         </is>
       </c>
     </row>
@@ -4474,16 +4470,16 @@
         <v>46286</v>
       </c>
       <c r="B87" s="9" t="n">
-        <v>7414</v>
+        <v>5910</v>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
@@ -4492,10 +4488,10 @@
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>44148.4</v>
+        <v>2865456.3</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>0</v>
+        <v>454972.35</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4511,23 +4507,27 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K87" s="12" t="inlineStr"/>
+      <c r="K87" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1119237.26</v>
+        <v>44148.4</v>
       </c>
       <c r="G88" s="10" t="n">
         <v>0</v>
@@ -4576,11 +4576,11 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>371982.96</v>
+        <v>1119237.26</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>
@@ -4603,28 +4603,28 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>7244</v>
+        <v>6352</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>132708.6</v>
+        <v>371982.96</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4647,31 +4647,31 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>7414</v>
+        <v>8304</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>-26 ГШ Фундамент домобудування Валерій Гибаленко</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>57497.5</v>
+        <v>55245</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>0</v>
+        <v>55245</v>
       </c>
       <c r="H91" s="11">
         <f>F91-G91</f>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4691,14 +4691,14 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>4766</v>
+        <v>7244</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1263447.42</v>
+        <v>132708.6</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4728,21 +4728,21 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K92" s="12" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>6024</v>
+        <v>7414</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>246402</v>
+        <v>57497.5</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4772,26 +4772,26 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K93" s="12" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46300</v>
+        <v>46295</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>6024</v>
+        <v>8304</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>-26 ГШ Фундамент домобудування Валерій Гибаленко</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3999</v>
+        <v>55245</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>0</v>
+        <v>55245</v>
       </c>
       <c r="H94" s="11">
         <f>F94-G94</f>
@@ -4811,40 +4811,40 @@
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46311</v>
+        <v>46297</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>8497</v>
+        <v>4766</v>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>518963.25</v>
+        <v>1263447.42</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -4863,27 +4863,23 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K95" s="12" t="inlineStr">
-        <is>
-          <t>€10 075</t>
-        </is>
-      </c>
+      <c r="K95" s="12" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46316</v>
+        <v>46300</v>
       </c>
       <c r="B96" s="9" t="n">
-        <v>6356</v>
+        <v>6024</v>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
@@ -4892,7 +4888,7 @@
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>3309002.4</v>
+        <v>246402</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -4911,36 +4907,32 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K96" s="12" t="inlineStr">
-        <is>
-          <t>€64 240</t>
-        </is>
-      </c>
+      <c r="K96" s="12" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>46317</v>
+        <v>46300</v>
       </c>
       <c r="B97" s="9" t="n">
-        <v>7894</v>
+        <v>6024</v>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>737597.4</v>
+        <v>3999</v>
       </c>
       <c r="G97" s="10" t="n">
         <v>0</v>
@@ -4963,28 +4955,28 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46321</v>
+        <v>46311</v>
       </c>
       <c r="B98" s="9" t="n">
-        <v>6352</v>
+        <v>8497</v>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>651792.28</v>
+        <v>518358.75</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -5003,11 +4995,15 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K98" s="12" t="inlineStr"/>
+      <c r="K98" s="12" t="inlineStr">
+        <is>
+          <t>€10 075</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>46322</v>
+        <v>46316</v>
       </c>
       <c r="B99" s="9" t="n">
         <v>6356</v>
@@ -5024,11 +5020,11 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>661800.48</v>
+        <v>3305148</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
@@ -5049,34 +5045,34 @@
       </c>
       <c r="K99" s="12" t="inlineStr">
         <is>
-          <t>€12 848</t>
+          <t>€64 240</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46343</v>
+        <v>46317</v>
       </c>
       <c r="B100" s="9" t="n">
-        <v>8238</v>
+        <v>7894</v>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>550000</v>
+        <v>737597.4</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
@@ -5092,32 +5088,168 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B101" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>АБМК SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="11">
+        <f>F101-G101</f>
+        <v/>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K101" s="12" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B102" s="9" t="n">
+        <v>6356</v>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>Хома</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>661029.6000000001</v>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="11">
+        <f>F102-G102</f>
+        <v/>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K102" s="12" t="inlineStr">
+        <is>
+          <t>€12 848</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="n">
+        <v>46343</v>
+      </c>
+      <c r="B103" s="9" t="n">
+        <v>8238</v>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>Іщук</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="n">
+        <v>550000</v>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="11">
+        <f>F103-G103</f>
+        <v/>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="K100" s="12" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="E101" s="3" t="inlineStr">
+      <c r="K103" s="12" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F101" s="13">
-        <f>SUM(F2:F100)</f>
-        <v/>
-      </c>
-      <c r="G101" s="13">
-        <f>SUM(G2:G100)</f>
-        <v/>
-      </c>
-      <c r="H101" s="13">
-        <f>SUM(H2:H100)</f>
+      <c r="F104" s="13">
+        <f>SUM(F2:F103)</f>
+        <v/>
+      </c>
+      <c r="G104" s="13">
+        <f>SUM(G2:G103)</f>
+        <v/>
+      </c>
+      <c r="H104" s="13">
+        <f>SUM(H2:H103)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I100"/>
+  <autoFilter ref="A1:I103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 17.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 18.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -4243,14 +4243,14 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="B82" s="9" t="n">
-        <v>8898</v>
+        <v>8304</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>-26 ГШ Фундамент домобудування Валерій Гибаленко</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
@@ -4260,14 +4260,14 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F82" s="10" t="n">
-        <v>188043.75</v>
+        <v>55245</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>0</v>
+        <v>55245</v>
       </c>
       <c r="H82" s="11">
         <f>F82-G82</f>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4287,14 +4287,14 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="B83" s="9" t="n">
-        <v>7002</v>
+        <v>8304</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>-26 ГШ Фундамент домобудування Валерій Гибаленко</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
@@ -4304,14 +4304,14 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F83" s="10" t="n">
-        <v>573945</v>
+        <v>55245</v>
       </c>
       <c r="G83" s="10" t="n">
-        <v>0</v>
+        <v>55245</v>
       </c>
       <c r="H83" s="11">
         <f>F83-G83</f>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4334,25 +4334,25 @@
         <v>46283</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>7002</v>
+        <v>7508</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>257000</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4378,16 +4378,16 @@
         <v>46283</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>7508</v>
+        <v>8898</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>188043.75</v>
       </c>
       <c r="G85" s="10" t="n">
         <v>0</v>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4422,28 +4422,28 @@
         <v>46286</v>
       </c>
       <c r="B86" s="9" t="n">
-        <v>5910</v>
+        <v>7414</v>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>17193612.45</v>
+        <v>44148.4</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>7171152.45</v>
+        <v>0</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4459,15 +4459,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K86" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K86" s="12" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B87" s="9" t="n">
         <v>5910</v>
@@ -4484,14 +4480,14 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>2865456.3</v>
+        <v>17193612.45</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>454972.35</v>
+        <v>10929574.95</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4509,25 +4505,25 @@
       </c>
       <c r="K87" s="12" t="inlineStr">
         <is>
-          <t>€55 694</t>
+          <t>€334 181</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>7414</v>
+        <v>5910</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
@@ -4536,10 +4532,10 @@
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>44148.4</v>
+        <v>2865456.3</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>0</v>
+        <v>1366563.45</v>
       </c>
       <c r="H88" s="11">
         <f>F88-G88</f>
@@ -4555,18 +4551,22 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K88" s="12" t="inlineStr"/>
+      <c r="K88" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>6352</v>
+        <v>7002</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
@@ -4576,11 +4576,11 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>1119237.26</v>
+        <v>573945</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>
@@ -4603,14 +4603,14 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>6352</v>
+        <v>7002</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -4620,11 +4620,11 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>371982.96</v>
+        <v>257000</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4647,14 +4647,14 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>8304</v>
+        <v>6352</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Валерій Гибаленко</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -4664,14 +4664,14 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>55245</v>
+        <v>1119237.26</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>55245</v>
+        <v>0</v>
       </c>
       <c r="H91" s="11">
         <f>F91-G91</f>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4691,28 +4691,28 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>7244</v>
+        <v>6352</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>132708.6</v>
+        <v>371982.96</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4738,11 +4738,11 @@
         <v>46295</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>7414</v>
+        <v>7244</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>57497.5</v>
+        <v>132708.6</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4782,28 +4782,28 @@
         <v>46295</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>8304</v>
+        <v>7414</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Валерій Гибаленко</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>55245</v>
+        <v>57497.5</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>55245</v>
+        <v>0</v>
       </c>
       <c r="H94" s="11">
         <f>F94-G94</f>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5051,14 +5051,14 @@
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46317</v>
+        <v>46321</v>
       </c>
       <c r="B100" s="9" t="n">
-        <v>7894</v>
+        <v>6352</v>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>737597.4</v>
+        <v>651792.28</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
@@ -5095,28 +5095,28 @@
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B101" s="9" t="n">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F101" s="10" t="n">
-        <v>651792.28</v>
+        <v>661029.6000000001</v>
       </c>
       <c r="G101" s="10" t="n">
         <v>0</v>
@@ -5135,32 +5135,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K101" s="12" t="inlineStr"/>
+      <c r="K101" s="12" t="inlineStr">
+        <is>
+          <t>€12 848</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B102" s="9" t="n">
-        <v>6356</v>
+        <v>7894</v>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F102" s="10" t="n">
-        <v>661029.6000000001</v>
+        <v>737597.4</v>
       </c>
       <c r="G102" s="10" t="n">
         <v>0</v>
@@ -5179,11 +5183,7 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K102" s="12" t="inlineStr">
-        <is>
-          <t>€12 848</t>
-        </is>
-      </c>
+      <c r="K102" s="12" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
@@ -5515,7 +5515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5566,14 +5566,14 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>8898</v>
+        <v>7508</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>188043.75</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5594,26 +5594,26 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46260</v>
+        <v>46283</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6406</v>
+        <v>8898</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>218602</v>
+        <v>188043.75</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -5621,26 +5621,54 @@
       </c>
     </row>
     <row r="4">
-      <c r="D4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>170788</v>
+      </c>
+      <c r="G4" s="11">
+        <f>E4-F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E4" s="13">
-        <f>SUM(E2:E3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>SUM(F2:F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>SUM(G2:G3)</f>
+      <c r="E5" s="13">
+        <f>SUM(E2:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="13">
+        <f>SUM(F2:F4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="13">
+        <f>SUM(G2:G4)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 18.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 21.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2572500</v>
+        <v>2560000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2572500</v>
+        <v>2560000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5145000</v>
+        <v>5120000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5145000</v>
+        <v>5120000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1852200</v>
+        <v>1843200</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1852200</v>
+        <v>1843200</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>452760</v>
+        <v>450560</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>452760</v>
+        <v>450560</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8596780.5</v>
+        <v>8555008</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8596780.5</v>
+        <v>8555008</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4049115</v>
+        <v>4029440</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4049115</v>
+        <v>4029440</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4925051.25</v>
+        <v>4901120</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4925051.25</v>
+        <v>4901120</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>749883.75</v>
+        <v>746240</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>749883.75</v>
+        <v>746240</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>556431.75</v>
+        <v>553728</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>556431.75</v>
+        <v>553728</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>900375</v>
+        <v>896000</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>900375</v>
+        <v>896000</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2801761.2</v>
+        <v>2788147.2</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>2801761.2</v>
+        <v>2788147.2</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1555076.25</v>
+        <v>1547520</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>1555076.25</v>
+        <v>1547520</v>
       </c>
       <c r="H80" s="11">
         <f>F80-G80</f>
@@ -4334,16 +4334,16 @@
         <v>46283</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>7508</v>
+        <v>8898</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>188043.75</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4375,19 +4375,19 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>8898</v>
+        <v>7414</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>188043.75</v>
+        <v>44148.4</v>
       </c>
       <c r="G85" s="10" t="n">
         <v>0</v>
@@ -4419,31 +4419,31 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B86" s="9" t="n">
-        <v>7414</v>
+        <v>5910</v>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>44148.4</v>
+        <v>17110067.2</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>0</v>
+        <v>10876467.2</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4459,7 +4459,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K86" s="12" t="inlineStr"/>
+      <c r="K86" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
@@ -4480,14 +4484,14 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>17193612.45</v>
+        <v>2851532.8</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>10929574.95</v>
+        <v>1359923.2</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4505,7 +4509,7 @@
       </c>
       <c r="K87" s="12" t="inlineStr">
         <is>
-          <t>€334 181</t>
+          <t>€55 694</t>
         </is>
       </c>
     </row>
@@ -4514,11 +4518,11 @@
         <v>46288</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
@@ -4528,14 +4532,14 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>2865456.3</v>
+        <v>492945</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>1366563.45</v>
+        <v>492945</v>
       </c>
       <c r="H88" s="11">
         <f>F88-G88</f>
@@ -4543,7 +4547,7 @@
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4551,11 +4555,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K88" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K88" s="12" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
@@ -4576,14 +4576,14 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>573945</v>
+        <v>338000</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>0</v>
+        <v>338000</v>
       </c>
       <c r="H89" s="11">
         <f>F89-G89</f>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4603,14 +4603,14 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>7002</v>
+        <v>6352</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
@@ -4620,11 +4620,11 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>257000</v>
+        <v>1119237.26</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4664,11 +4664,11 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>1119237.26</v>
+        <v>371982.96</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4691,28 +4691,28 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>6352</v>
+        <v>7244</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>371982.96</v>
+        <v>132708.6</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4738,11 +4738,11 @@
         <v>46295</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>7244</v>
+        <v>7414</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>132708.6</v>
+        <v>57497.5</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4779,14 +4779,14 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>7414</v>
+        <v>4766</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -4796,11 +4796,11 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>57497.5</v>
+        <v>1263447.42</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -4816,21 +4816,21 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>4766</v>
+        <v>6024</v>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -4840,11 +4840,11 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>1263447.42</v>
+        <v>246402</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -4884,11 +4884,11 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>246402</v>
+        <v>3999</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -4911,28 +4911,28 @@
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="B97" s="9" t="n">
-        <v>6024</v>
+        <v>8497</v>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>3999</v>
+        <v>515840</v>
       </c>
       <c r="G97" s="10" t="n">
         <v>0</v>
@@ -4951,23 +4951,27 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K97" s="12" t="inlineStr"/>
+      <c r="K97" s="12" t="inlineStr">
+        <is>
+          <t>€10 075</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B98" s="9" t="n">
-        <v>8497</v>
+        <v>6356</v>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -4976,7 +4980,7 @@
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>518358.75</v>
+        <v>3289088</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -4997,34 +5001,34 @@
       </c>
       <c r="K98" s="12" t="inlineStr">
         <is>
-          <t>€10 075</t>
+          <t>€64 240</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="B99" s="9" t="n">
-        <v>6356</v>
+        <v>6352</v>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>3305148</v>
+        <v>651792.28</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
@@ -5043,36 +5047,32 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K99" s="12" t="inlineStr">
-        <is>
-          <t>€64 240</t>
-        </is>
-      </c>
+      <c r="K99" s="12" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B100" s="9" t="n">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>651792.28</v>
+        <v>657817.6000000001</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
@@ -5091,32 +5091,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K100" s="12" t="inlineStr"/>
+      <c r="K100" s="12" t="inlineStr">
+        <is>
+          <t>€12 848</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B101" s="9" t="n">
-        <v>6356</v>
+        <v>7894</v>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F101" s="10" t="n">
-        <v>661029.6000000001</v>
+        <v>737597.4</v>
       </c>
       <c r="G101" s="10" t="n">
         <v>0</v>
@@ -5135,36 +5139,32 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K101" s="12" t="inlineStr">
-        <is>
-          <t>€12 848</t>
-        </is>
-      </c>
+      <c r="K101" s="12" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>46322</v>
+        <v>46330</v>
       </c>
       <c r="B102" s="9" t="n">
-        <v>7894</v>
+        <v>7508</v>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F102" s="10" t="n">
-        <v>737597.4</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G102" s="10" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="K102" s="12" t="inlineStr"/>
@@ -5569,11 +5569,11 @@
         <v>46283</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>7508</v>
+        <v>8898</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>750999.9399999999</v>
+        <v>188043.75</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5594,26 +5594,26 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46283</v>
+        <v>46260</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>8898</v>
+        <v>6406</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>188043.75</v>
+        <v>218602</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -5622,26 +5622,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46260</v>
+        <v>46286</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6406</v>
+        <v>7414</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>218602</v>
+        <v>44148.4</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 21.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 22.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2560000</v>
+        <v>2568500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2560000</v>
+        <v>2568500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5120000</v>
+        <v>5137000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5120000</v>
+        <v>5137000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1843200</v>
+        <v>1849320</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1843200</v>
+        <v>1849320</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>450560</v>
+        <v>452056</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>450560</v>
+        <v>452056</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8555008</v>
+        <v>8583413.299999999</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8555008</v>
+        <v>8583413.299999999</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4029440</v>
+        <v>4042819</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4029440</v>
+        <v>4042819</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4901120</v>
+        <v>4917393.25</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4901120</v>
+        <v>4917393.25</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>746240</v>
+        <v>748717.75</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>746240</v>
+        <v>748717.75</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>553728</v>
+        <v>555566.5499999999</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>553728</v>
+        <v>555566.5499999999</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>896000</v>
+        <v>898975</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>896000</v>
+        <v>898975</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2788147.2</v>
+        <v>2797404.72</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>2788147.2</v>
+        <v>2797404.72</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1547520</v>
+        <v>1552658.25</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>1547520</v>
+        <v>1552658.25</v>
       </c>
       <c r="H80" s="11">
         <f>F80-G80</f>
@@ -4331,19 +4331,19 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>8898</v>
+        <v>7414</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>188043.75</v>
+        <v>44148.4</v>
       </c>
       <c r="G84" s="10" t="n">
         <v>0</v>
@@ -4375,31 +4375,31 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>7414</v>
+        <v>5910</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>44148.4</v>
+        <v>17166877.97</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>0</v>
+        <v>10912580.47</v>
       </c>
       <c r="H85" s="11">
         <f>F85-G85</f>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4415,7 +4415,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K85" s="12" t="inlineStr"/>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
@@ -4436,14 +4440,14 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>17110067.2</v>
+        <v>2861000.78</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>10876467.2</v>
+        <v>1364438.57</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>€334 181</t>
+          <t>€55 694</t>
         </is>
       </c>
     </row>
@@ -4470,11 +4474,11 @@
         <v>46288</v>
       </c>
       <c r="B87" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
@@ -4484,14 +4488,14 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>2851532.8</v>
+        <v>492945</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>1359923.2</v>
+        <v>492945</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4499,7 +4503,7 @@
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4507,11 +4511,7 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K87" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K87" s="12" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
@@ -4532,14 +4532,14 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>492945</v>
+        <v>338000</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>492945</v>
+        <v>338000</v>
       </c>
       <c r="H88" s="11">
         <f>F88-G88</f>
@@ -4562,11 +4562,11 @@
         <v>46288</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>7002</v>
+        <v>8898</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
@@ -4576,14 +4576,14 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>338000</v>
+        <v>188043.75</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>338000</v>
+        <v>0</v>
       </c>
       <c r="H89" s="11">
         <f>F89-G89</f>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4603,19 +4603,19 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>6352</v>
+        <v>8238</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>1119237.26</v>
+        <v>550000</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4664,11 +4664,11 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>371982.96</v>
+        <v>1119237.26</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4691,28 +4691,28 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>7244</v>
+        <v>6352</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>132708.6</v>
+        <v>371982.96</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4738,11 +4738,11 @@
         <v>46295</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>7414</v>
+        <v>7244</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>57497.5</v>
+        <v>132708.6</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4779,14 +4779,14 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>4766</v>
+        <v>7414</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -4796,11 +4796,11 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>1263447.42</v>
+        <v>57497.5</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -4816,21 +4816,21 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="K94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>6024</v>
+        <v>4766</v>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -4840,11 +4840,11 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>246402</v>
+        <v>1263447.42</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -4884,11 +4884,11 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>3999</v>
+        <v>246402</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -4911,28 +4911,28 @@
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>46311</v>
+        <v>46300</v>
       </c>
       <c r="B97" s="9" t="n">
-        <v>8497</v>
+        <v>6024</v>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>515840</v>
+        <v>3999</v>
       </c>
       <c r="G97" s="10" t="n">
         <v>0</v>
@@ -4951,27 +4951,23 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K97" s="12" t="inlineStr">
-        <is>
-          <t>€10 075</t>
-        </is>
-      </c>
+      <c r="K97" s="12" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46316</v>
+        <v>46311</v>
       </c>
       <c r="B98" s="9" t="n">
-        <v>6356</v>
+        <v>8497</v>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -4980,7 +4976,7 @@
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3289088</v>
+        <v>517552.75</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -5001,34 +4997,34 @@
       </c>
       <c r="K98" s="12" t="inlineStr">
         <is>
-          <t>€64 240</t>
+          <t>€10 075</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>46321</v>
+        <v>46316</v>
       </c>
       <c r="B99" s="9" t="n">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>651792.28</v>
+        <v>3300008.8</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
@@ -5047,32 +5043,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K99" s="12" t="inlineStr"/>
+      <c r="K99" s="12" t="inlineStr">
+        <is>
+          <t>€64 240</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="B100" s="9" t="n">
-        <v>6356</v>
+        <v>6352</v>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>657817.6000000001</v>
+        <v>651792.28</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
@@ -5091,36 +5091,32 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K100" s="12" t="inlineStr">
-        <is>
-          <t>€12 848</t>
-        </is>
-      </c>
+      <c r="K100" s="12" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B101" s="9" t="n">
-        <v>7894</v>
+        <v>6356</v>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F101" s="10" t="n">
-        <v>737597.4</v>
+        <v>660001.76</v>
       </c>
       <c r="G101" s="10" t="n">
         <v>0</v>
@@ -5139,32 +5135,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K101" s="12" t="inlineStr"/>
+      <c r="K101" s="12" t="inlineStr">
+        <is>
+          <t>€12 848</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>46330</v>
+        <v>46322</v>
       </c>
       <c r="B102" s="9" t="n">
-        <v>7508</v>
+        <v>7894</v>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F102" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>737597.4</v>
       </c>
       <c r="G102" s="10" t="n">
         <v>0</v>
@@ -5180,26 +5180,26 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K102" s="12" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
-        <v>46343</v>
+        <v>46330</v>
       </c>
       <c r="B103" s="9" t="n">
-        <v>8238</v>
+        <v>7508</v>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="F103" s="10" t="n">
-        <v>550000</v>
+        <v>750999.9399999999</v>
       </c>
       <c r="G103" s="10" t="n">
         <v>0</v>
@@ -5515,7 +5515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5566,26 +5566,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46283</v>
+        <v>46260</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>8898</v>
+        <v>6406</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>188043.75</v>
+        <v>218602</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -5594,26 +5594,26 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46260</v>
+        <v>46287</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6406</v>
+        <v>7414</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>218602</v>
+        <v>44148.4</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -5621,54 +5621,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>7414</v>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>44148.4</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="11">
-        <f>E4-F4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E5" s="13">
-        <f>SUM(E2:E4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>SUM(F2:F4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>SUM(G2:G4)</f>
+      <c r="E4" s="13">
+        <f>SUM(E2:E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="13">
+        <f>SUM(F2:F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="13">
+        <f>SUM(G2:G3)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 22.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 25.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2568500</v>
+        <v>2556000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2568500</v>
+        <v>2556000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5137000</v>
+        <v>5112000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5137000</v>
+        <v>5112000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1849320</v>
+        <v>1840320</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1849320</v>
+        <v>1840320</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>452056</v>
+        <v>449856</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>452056</v>
+        <v>449856</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8583413.299999999</v>
+        <v>8541640.799999999</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8583413.299999999</v>
+        <v>8541640.799999999</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4042819</v>
+        <v>4023144</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4042819</v>
+        <v>4023144</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4917393.25</v>
+        <v>4893462</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4917393.25</v>
+        <v>4893462</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>748717.75</v>
+        <v>745074</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>748717.75</v>
+        <v>745074</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>555566.5499999999</v>
+        <v>552862.7999999999</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>555566.5499999999</v>
+        <v>552862.7999999999</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>898975</v>
+        <v>894600</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>898975</v>
+        <v>894600</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2797404.72</v>
+        <v>2783790.72</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>2797404.72</v>
+        <v>2783790.72</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1552658.25</v>
+        <v>1545102</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>1552658.25</v>
+        <v>1545102</v>
       </c>
       <c r="H80" s="11">
         <f>F80-G80</f>
@@ -4334,16 +4334,16 @@
         <v>46287</v>
       </c>
       <c r="B84" s="9" t="n">
-        <v>7414</v>
+        <v>8898</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>Григорівка №3</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="F84" s="10" t="n">
-        <v>44148.4</v>
+        <v>188043.75</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>0</v>
+        <v>188043.75</v>
       </c>
       <c r="H84" s="11">
         <f>F84-G84</f>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>17166877.97</v>
+        <v>17083332.72</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>10912580.47</v>
+        <v>10859472.72</v>
       </c>
       <c r="H85" s="11">
         <f>F85-G85</f>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>2861000.78</v>
+        <v>2847077.28</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>1364438.57</v>
+        <v>1357798.32</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4559,19 +4559,19 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>8898</v>
+        <v>8238</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Григорівка №3</t>
+          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>188043.75</v>
+        <v>550000</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4603,19 +4603,19 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>8238</v>
+        <v>6352</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>550000</v>
+        <v>1119237.26</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4664,11 +4664,11 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>1119237.26</v>
+        <v>371982.96</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4691,28 +4691,28 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>6352</v>
+        <v>7244</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>371982.96</v>
+        <v>132708.6</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4738,11 +4738,11 @@
         <v>46295</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>7244</v>
+        <v>7414</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>132708.6</v>
+        <v>44148.4</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>517552.75</v>
+        <v>515034</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>3300008.8</v>
+        <v>3283948.8</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="F101" s="10" t="n">
-        <v>660001.76</v>
+        <v>656789.76</v>
       </c>
       <c r="G101" s="10" t="n">
         <v>0</v>
@@ -5515,7 +5515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5566,26 +5566,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46260</v>
+        <v>46288</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>6406</v>
+        <v>5910</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>218602</v>
+        <v>17083332.72</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>170788</v>
+        <v>10859472.72</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -5594,14 +5594,14 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>7414</v>
+        <v>5910</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>44148.4</v>
+        <v>2847077.28</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>0</v>
+        <v>1357798.32</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -5621,26 +5621,82 @@
       </c>
     </row>
     <row r="4">
-      <c r="D4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>8238</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>550000</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="11">
+        <f>E4-F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>170788</v>
+      </c>
+      <c r="G5" s="11">
+        <f>E5-F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E4" s="13">
-        <f>SUM(E2:E3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="13">
-        <f>SUM(F2:F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="13">
-        <f>SUM(G2:G3)</f>
+      <c r="E6" s="13">
+        <f>SUM(E2:E5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="13">
+        <f>SUM(F2:F5)</f>
+        <v/>
+      </c>
+      <c r="G6" s="13">
+        <f>SUM(G2:G5)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 25.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 28.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2556000</v>
+        <v>2557000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2556000</v>
+        <v>2557000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5112000</v>
+        <v>5114000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5112000</v>
+        <v>5114000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>2011000</v>
+        <v>45700</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>2011000</v>
+        <v>45700</v>
       </c>
       <c r="H15" s="11">
         <f>F15-G15</f>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1840320</v>
+        <v>1841040</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1840320</v>
+        <v>1841040</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>449856</v>
+        <v>450032</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>449856</v>
+        <v>450032</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8541640.799999999</v>
+        <v>8544982.6</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8541640.799999999</v>
+        <v>8544982.6</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4023144</v>
+        <v>4024718</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4023144</v>
+        <v>4024718</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3536,10 +3536,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4893462</v>
+        <v>4895376.5</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4893462</v>
+        <v>4895376.5</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>745074</v>
+        <v>745365.5</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>745074</v>
+        <v>745365.5</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>552862.7999999999</v>
+        <v>553079.1</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>552862.7999999999</v>
+        <v>553079.1</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>894600</v>
+        <v>894950</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>894600</v>
+        <v>894950</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2783790.72</v>
+        <v>2784879.84</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>2783790.72</v>
+        <v>2784879.84</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1545102</v>
+        <v>1545706.5</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>1545102</v>
+        <v>1545706.5</v>
       </c>
       <c r="H80" s="11">
         <f>F80-G80</f>
@@ -4378,11 +4378,11 @@
         <v>46288</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
@@ -4392,14 +4392,14 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F85" s="10" t="n">
-        <v>17083332.72</v>
+        <v>492945</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>10859472.72</v>
+        <v>492945</v>
       </c>
       <c r="H85" s="11">
         <f>F85-G85</f>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4415,22 +4415,18 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K85" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K85" s="12" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
         <v>46288</v>
       </c>
       <c r="B86" s="9" t="n">
-        <v>5910</v>
+        <v>7002</v>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Фора SCP Млиново</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
@@ -4440,14 +4436,14 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Шостий платіж (Допка)</t>
         </is>
       </c>
       <c r="F86" s="10" t="n">
-        <v>2847077.28</v>
+        <v>338000</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>1357798.32</v>
+        <v>338000</v>
       </c>
       <c r="H86" s="11">
         <f>F86-G86</f>
@@ -4455,7 +4451,7 @@
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4463,39 +4459,35 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K86" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K86" s="12" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B87" s="9" t="n">
-        <v>7002</v>
+        <v>8238</v>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>492945</v>
+        <v>12900</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>492945</v>
+        <v>12900</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4515,31 +4507,31 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>7002</v>
+        <v>7244</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Фора SCP Млиново</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Шостий платіж (Допка)</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>338000</v>
+        <v>132708.6</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>338000</v>
+        <v>0</v>
       </c>
       <c r="H88" s="11">
         <f>F88-G88</f>
@@ -4547,7 +4539,7 @@
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4559,19 +4551,19 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B89" s="9" t="n">
-        <v>8238</v>
+        <v>7414</v>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -4580,7 +4572,7 @@
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>550000</v>
+        <v>44148.4</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>
@@ -4591,7 +4583,7 @@
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4603,28 +4595,28 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>1119237.26</v>
+        <v>57497.5</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
@@ -4647,28 +4639,28 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>6352</v>
+        <v>4766</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>371982.96</v>
+        <v>1263447.42</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4684,38 +4676,38 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K91" s="12" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>7244</v>
+        <v>5910</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>132708.6</v>
+        <v>17090016.34</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>0</v>
+        <v>15844757.34</v>
       </c>
       <c r="H92" s="11">
         <f>F92-G92</f>
@@ -4728,26 +4720,30 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="K92" s="12" t="inlineStr"/>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K92" s="12" t="inlineStr">
+        <is>
+          <t>€334 181</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>7414</v>
+        <v>5910</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
@@ -4756,10 +4752,10 @@
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>44148.4</v>
+        <v>2848191.16</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>0</v>
+        <v>1358329.54</v>
       </c>
       <c r="H93" s="11">
         <f>F93-G93</f>
@@ -4772,21 +4768,25 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="K93" s="12" t="inlineStr"/>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>7414</v>
+        <v>6024</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -4796,11 +4796,11 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>57497.5</v>
+        <v>246402</v>
       </c>
       <c r="G94" s="10" t="n">
         <v>0</v>
@@ -4816,21 +4816,21 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>4766</v>
+        <v>6024</v>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -4840,11 +4840,11 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>1263447.42</v>
+        <v>3999</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -4867,28 +4867,28 @@
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46300</v>
+        <v>46310</v>
       </c>
       <c r="B96" s="9" t="n">
-        <v>6024</v>
+        <v>6352</v>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>246402</v>
+        <v>1119237.26</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -4911,28 +4911,28 @@
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>46300</v>
+        <v>46310</v>
       </c>
       <c r="B97" s="9" t="n">
-        <v>6024</v>
+        <v>6352</v>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>3999</v>
+        <v>371982.96</v>
       </c>
       <c r="G97" s="10" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>515034</v>
+        <v>515235.5</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>3283948.8</v>
+        <v>3285233.6</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="F101" s="10" t="n">
-        <v>656789.76</v>
+        <v>657046.72</v>
       </c>
       <c r="G101" s="10" t="n">
         <v>0</v>
@@ -5515,7 +5515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5566,26 +5566,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46288</v>
+        <v>46260</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5910</v>
+        <v>6406</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>17083332.72</v>
+        <v>218602</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>10859472.72</v>
+        <v>170788</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -5593,110 +5593,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>5910</v>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>SGM Brdovec, Хорватия</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>2847077.28</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>1357798.32</v>
-      </c>
-      <c r="G3" s="11">
-        <f>E3-F3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>8238</v>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>А UTEM SOLAR  SCP Taurus 190PV</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>Третій платіж</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>550000</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="11">
-        <f>E4-F4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>6406</v>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Максим Яловий Чинадієво</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>218602</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>170788</v>
-      </c>
-      <c r="G5" s="11">
-        <f>E5-F5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E6" s="13">
-        <f>SUM(E2:E5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="13">
-        <f>SUM(F2:F5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>SUM(G2:G5)</f>
+      <c r="E3" s="13">
+        <f>SUM(E2:E2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="13">
+        <f>SUM(F2:F2)</f>
+        <v/>
+      </c>
+      <c r="G3" s="13">
+        <f>SUM(G2:G2)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>45700</v>
+        <v>2049188</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>45700</v>
+        <v>2049188</v>
       </c>
       <c r="H15" s="11">
         <f>F15-G15</f>
@@ -1295,7 +1295,11 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="K15" s="12" t="inlineStr"/>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>$45 700</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -4484,10 +4488,10 @@
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>12900</v>
+        <v>578436</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>12900</v>
+        <v>578436</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4503,7 +4507,11 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K87" s="12" t="inlineStr"/>
+      <c r="K87" s="12" t="inlineStr">
+        <is>
+          <t>$12 900</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 28.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 29.09.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2557000</v>
+        <v>2548500</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2557000</v>
+        <v>2548500</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5114000</v>
+        <v>5097000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5114000</v>
+        <v>5097000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>2049188</v>
+        <v>2048274</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>2049188</v>
+        <v>2048274</v>
       </c>
       <c r="H15" s="11">
         <f>F15-G15</f>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1841040</v>
+        <v>1834920</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1841040</v>
+        <v>1834920</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>450032</v>
+        <v>448536</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>450032</v>
+        <v>448536</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8544982.6</v>
+        <v>8516577.299999999</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8544982.6</v>
+        <v>8516577.299999999</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4024718</v>
+        <v>4011339</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4024718</v>
+        <v>4011339</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4895376.5</v>
+        <v>4879103.25</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4895376.5</v>
+        <v>4879103.25</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>745365.5</v>
+        <v>742887.75</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>745365.5</v>
+        <v>742887.75</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>553079.1</v>
+        <v>551240.5499999999</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>553079.1</v>
+        <v>551240.5499999999</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>894950</v>
+        <v>891975</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>894950</v>
+        <v>891975</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -4084,10 +4084,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2784879.84</v>
+        <v>2775622.32</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>2784879.84</v>
+        <v>2775622.32</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1545706.5</v>
+        <v>1540568.25</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>1545706.5</v>
+        <v>1540568.25</v>
       </c>
       <c r="H80" s="11">
         <f>F80-G80</f>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>578436</v>
+        <v>578178</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>578436</v>
+        <v>578178</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>17090016.34</v>
+        <v>17033205.57</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>15844757.34</v>
+        <v>15792086.07</v>
       </c>
       <c r="H92" s="11">
         <f>F92-G92</f>
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>2848191.16</v>
+        <v>2838723.18</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>1358329.54</v>
+        <v>1353814.17</v>
       </c>
       <c r="H93" s="11">
         <f>F93-G93</f>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>515235.5</v>
+        <v>513522.75</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>3285233.6</v>
+        <v>3274312.8</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
@@ -5124,7 +5124,7 @@
         </is>
       </c>
       <c r="F101" s="10" t="n">
-        <v>657046.72</v>
+        <v>654862.5599999999</v>
       </c>
       <c r="G101" s="10" t="n">
         <v>0</v>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 29.09.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 01.10.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2548500</v>
+        <v>2588000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2548500</v>
+        <v>2588000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5097000</v>
+        <v>5176000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5097000</v>
+        <v>5176000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>2048274</v>
+        <v>2035935</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>2048274</v>
+        <v>2035935</v>
       </c>
       <c r="H15" s="11">
         <f>F15-G15</f>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1834920</v>
+        <v>1863360</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1834920</v>
+        <v>1863360</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>448536</v>
+        <v>455488</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>448536</v>
+        <v>455488</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8516577.299999999</v>
+        <v>8648578.4</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8516577.299999999</v>
+        <v>8648578.4</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4011339</v>
+        <v>4073512</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4011339</v>
+        <v>4073512</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4879103.25</v>
+        <v>4954726</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4879103.25</v>
+        <v>4954726</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>742887.75</v>
+        <v>754402</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>742887.75</v>
+        <v>754402</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>551240.5499999999</v>
+        <v>559784.4</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>551240.5499999999</v>
+        <v>559784.4</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>891975</v>
+        <v>905800</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>891975</v>
+        <v>905800</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -4084,10 +4084,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2775622.32</v>
+        <v>2818642.56</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>2775622.32</v>
+        <v>2818642.56</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1540568.25</v>
+        <v>1564446</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>1540568.25</v>
+        <v>1564446</v>
       </c>
       <c r="H80" s="11">
         <f>F80-G80</f>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>578178</v>
+        <v>574695</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>578178</v>
+        <v>574695</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="F89" s="10" t="n">
-        <v>44148.4</v>
+        <v>50823</v>
       </c>
       <c r="G89" s="10" t="n">
         <v>0</v>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4606,28 +4606,28 @@
         <v>46295</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>7414</v>
+        <v>7904</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>А СОЛАРС РЕ ЕНЕРДЖІ ГРУП</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>57497.5</v>
+        <v>691660.98</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>0</v>
+        <v>691660.98</v>
       </c>
       <c r="H90" s="11">
         <f>F90-G90</f>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>17033205.57</v>
+        <v>17297208.56</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>15792086.07</v>
+        <v>16036852.56</v>
       </c>
       <c r="H92" s="11">
         <f>F92-G92</f>
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>2838723.18</v>
+        <v>2882721.44</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>1353814.17</v>
+        <v>1374797.36</v>
       </c>
       <c r="H93" s="11">
         <f>F93-G93</f>
@@ -4875,28 +4875,28 @@
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46310</v>
+        <v>46300</v>
       </c>
       <c r="B96" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>1119237.26</v>
+        <v>50822.9</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -4936,11 +4936,11 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>371982.96</v>
+        <v>1119237.26</v>
       </c>
       <c r="G97" s="10" t="n">
         <v>0</v>
@@ -4963,28 +4963,28 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B98" s="9" t="n">
-        <v>8497</v>
+        <v>6352</v>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>513522.75</v>
+        <v>371982.96</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -5003,27 +5003,23 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K98" s="12" t="inlineStr">
-        <is>
-          <t>€10 075</t>
-        </is>
-      </c>
+      <c r="K98" s="12" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>46316</v>
+        <v>46311</v>
       </c>
       <c r="B99" s="9" t="n">
-        <v>6356</v>
+        <v>8497</v>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
@@ -5032,7 +5028,7 @@
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>3274312.8</v>
+        <v>521482</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
@@ -5053,34 +5049,34 @@
       </c>
       <c r="K99" s="12" t="inlineStr">
         <is>
-          <t>€64 240</t>
+          <t>€10 075</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46321</v>
+        <v>46316</v>
       </c>
       <c r="B100" s="9" t="n">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>651792.28</v>
+        <v>3325062.4</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
@@ -5099,32 +5095,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K100" s="12" t="inlineStr"/>
+      <c r="K100" s="12" t="inlineStr">
+        <is>
+          <t>€64 240</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="B101" s="9" t="n">
-        <v>6356</v>
+        <v>6352</v>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F101" s="10" t="n">
-        <v>654862.5599999999</v>
+        <v>651792.28</v>
       </c>
       <c r="G101" s="10" t="n">
         <v>0</v>
@@ -5143,36 +5143,32 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K101" s="12" t="inlineStr">
-        <is>
-          <t>€12 848</t>
-        </is>
-      </c>
+      <c r="K101" s="12" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B102" s="9" t="n">
-        <v>7894</v>
+        <v>6356</v>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F102" s="10" t="n">
-        <v>737597.4</v>
+        <v>665012.48</v>
       </c>
       <c r="G102" s="10" t="n">
         <v>0</v>
@@ -5191,32 +5187,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K102" s="12" t="inlineStr"/>
+      <c r="K102" s="12" t="inlineStr">
+        <is>
+          <t>€12 848</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
-        <v>46330</v>
+        <v>46322</v>
       </c>
       <c r="B103" s="9" t="n">
-        <v>7508</v>
+        <v>7894</v>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F103" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>737597.4</v>
       </c>
       <c r="G103" s="10" t="n">
         <v>0</v>
@@ -5232,32 +5232,76 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K103" s="12" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B104" s="9" t="n">
+        <v>7508</v>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>750999.9399999999</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="11">
+        <f>F104-G104</f>
+        <v/>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="K103" s="12" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="E104" s="3" t="inlineStr">
+      <c r="K104" s="12" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F104" s="13">
-        <f>SUM(F2:F103)</f>
-        <v/>
-      </c>
-      <c r="G104" s="13">
-        <f>SUM(G2:G103)</f>
-        <v/>
-      </c>
-      <c r="H104" s="13">
-        <f>SUM(H2:H103)</f>
+      <c r="F105" s="13">
+        <f>SUM(F2:F104)</f>
+        <v/>
+      </c>
+      <c r="G105" s="13">
+        <f>SUM(G2:G104)</f>
+        <v/>
+      </c>
+      <c r="H105" s="13">
+        <f>SUM(H2:H104)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I103"/>
+  <autoFilter ref="A1:I104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5523,7 +5567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5574,26 +5618,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46260</v>
+        <v>46295</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>6406</v>
+        <v>7244</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>218602</v>
+        <v>132708.6</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -5601,26 +5645,82 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>7414</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>50823</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11">
+        <f>E3-F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>170788</v>
+      </c>
+      <c r="G4" s="11">
+        <f>E4-F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E3" s="13">
-        <f>SUM(E2:E2)</f>
-        <v/>
-      </c>
-      <c r="F3" s="13">
-        <f>SUM(F2:F2)</f>
-        <v/>
-      </c>
-      <c r="G3" s="13">
-        <f>SUM(G2:G2)</f>
+      <c r="E5" s="13">
+        <f>SUM(E2:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="13">
+        <f>SUM(F2:F4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="13">
+        <f>SUM(G2:G4)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 01.10.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 02.10.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5567,7 +5567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5618,14 +5618,14 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>7244</v>
+        <v>4766</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>132708.6</v>
+        <v>1263447.42</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5649,20 +5649,20 @@
         <v>46295</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>7414</v>
+        <v>7244</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>50823</v>
+        <v>132708.6</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -5674,26 +5674,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46260</v>
+        <v>46295</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6406</v>
+        <v>7414</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>218602</v>
+        <v>50823</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -5701,26 +5701,54 @@
       </c>
     </row>
     <row r="5">
-      <c r="D5" s="3" t="inlineStr">
+      <c r="A5" s="8" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Максим Яловий Чинадієво</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>218602</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>170788</v>
+      </c>
+      <c r="G5" s="11">
+        <f>E5-F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E5" s="13">
-        <f>SUM(E2:E4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>SUM(F2:F4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>SUM(G2:G4)</f>
+      <c r="E6" s="13">
+        <f>SUM(E2:E5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="13">
+        <f>SUM(F2:F5)</f>
+        <v/>
+      </c>
+      <c r="G6" s="13">
+        <f>SUM(G2:G5)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 02.10.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 03.10.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 03.10.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 05.10.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -4518,28 +4518,28 @@
         <v>46295</v>
       </c>
       <c r="B88" s="9" t="n">
-        <v>7244</v>
+        <v>7904</v>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>А СОЛАРС РЕ ЕНЕРДЖІ ГРУП</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F88" s="10" t="n">
-        <v>132708.6</v>
+        <v>691660.98</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>0</v>
+        <v>691660.98</v>
       </c>
       <c r="H88" s="11">
         <f>F88-G88</f>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4559,7 +4559,7 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B89" s="9" t="n">
         <v>7414</v>
@@ -4583,7 +4583,7 @@
         <v>50823</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>0</v>
+        <v>50823.44</v>
       </c>
       <c r="H89" s="11">
         <f>F89-G89</f>
@@ -4591,43 +4591,43 @@
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K89" s="12" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>7904</v>
+        <v>6024</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>А СОЛАРС РЕ ЕНЕРДЖІ ГРУП</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Авансовий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>691660.98</v>
+        <v>246402</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>691660.98</v>
+        <v>0</v>
       </c>
       <c r="H90" s="11">
         <f>F90-G90</f>
@@ -4635,26 +4635,26 @@
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>отримано</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>4766</v>
+        <v>6024</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -4664,11 +4664,11 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>1263447.42</v>
+        <v>3999</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4691,31 +4691,31 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>5910</v>
+        <v>7244</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>17297208.56</v>
+        <v>132708.6</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>16036852.56</v>
+        <v>0</v>
       </c>
       <c r="H92" s="11">
         <f>F92-G92</f>
@@ -4731,15 +4731,11 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K92" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K92" s="12" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="B93" s="9" t="n">
         <v>5910</v>
@@ -4756,14 +4752,14 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>2882721.44</v>
+        <v>17297208.56</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>1374797.36</v>
+        <v>16036852.56</v>
       </c>
       <c r="H93" s="11">
         <f>F93-G93</f>
@@ -4781,37 +4777,37 @@
       </c>
       <c r="K93" s="12" t="inlineStr">
         <is>
-          <t>€55 694</t>
+          <t>€334 181</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>6024</v>
+        <v>5910</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>246402</v>
+        <v>2882721.44</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>0</v>
+        <v>1374797.36</v>
       </c>
       <c r="H94" s="11">
         <f>F94-G94</f>
@@ -4827,18 +4823,22 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K94" s="12" t="inlineStr"/>
+      <c r="K94" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46300</v>
+        <v>46303</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>6024</v>
+        <v>4766</v>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -4848,11 +4848,11 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>3999</v>
+        <v>1263447.42</v>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
@@ -4875,7 +4875,7 @@
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46300</v>
+        <v>46309</v>
       </c>
       <c r="B96" s="9" t="n">
         <v>7414</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>50822.9</v>
+        <v>50822.46</v>
       </c>
       <c r="G96" s="10" t="n">
         <v>0</v>
@@ -5567,7 +5567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5618,23 +5618,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>4766</v>
+        <v>6024</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1263447.42</v>
+        <v>246402</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5646,26 +5646,26 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46295</v>
+        <v>46260</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>7244</v>
+        <v>6406</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>132708.6</v>
+        <v>218602</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -5674,14 +5674,14 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7414</v>
+        <v>6024</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>50823</v>
+        <v>3999</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>0</v>
@@ -5701,54 +5701,26 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>6406</v>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Максим Яловий Чинадієво</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>218602</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>170788</v>
-      </c>
-      <c r="G5" s="11">
-        <f>E5-F5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E6" s="13">
-        <f>SUM(E2:E5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="13">
-        <f>SUM(F2:F5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>SUM(G2:G5)</f>
+      <c r="E5" s="13">
+        <f>SUM(E2:E4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="13">
+        <f>SUM(F2:F4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="13">
+        <f>SUM(G2:G4)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 05.10.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 06.10.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B90" s="9" t="n">
         <v>6024</v>
@@ -4647,7 +4647,7 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B91" s="9" t="n">
         <v>6024</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5567,7 +5567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5618,7 +5618,7 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B2" s="9" t="n">
         <v>6024</v>
@@ -5646,26 +5646,26 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46260</v>
+        <v>46301</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6406</v>
+        <v>7244</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>218602</v>
+        <v>132708.6</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -5674,26 +5674,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46300</v>
+        <v>46260</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6024</v>
+        <v>6406</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>3999</v>
+        <v>218602</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -5701,26 +5701,54 @@
       </c>
     </row>
     <row r="5">
-      <c r="D5" s="3" t="inlineStr">
+      <c r="A5" s="8" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>6024</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>3999</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11">
+        <f>E5-F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E5" s="13">
-        <f>SUM(E2:E4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="13">
-        <f>SUM(F2:F4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>SUM(G2:G4)</f>
+      <c r="E6" s="13">
+        <f>SUM(E2:E5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="13">
+        <f>SUM(F2:F5)</f>
+        <v/>
+      </c>
+      <c r="G6" s="13">
+        <f>SUM(G2:G5)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 06.10.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 07.10.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -4735,31 +4735,31 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>5910</v>
+        <v>4766</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>17297208.56</v>
+        <v>1263447.42</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>16036852.56</v>
+        <v>0</v>
       </c>
       <c r="H93" s="11">
         <f>F93-G93</f>
@@ -4775,15 +4775,11 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K93" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K93" s="12" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="B94" s="9" t="n">
         <v>5910</v>
@@ -4800,14 +4796,14 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>2882721.44</v>
+        <v>17297208.56</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>1374797.36</v>
+        <v>16036852.56</v>
       </c>
       <c r="H94" s="11">
         <f>F94-G94</f>
@@ -4825,37 +4821,37 @@
       </c>
       <c r="K94" s="12" t="inlineStr">
         <is>
-          <t>€55 694</t>
+          <t>€334 181</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>1263447.42</v>
+        <v>2882721.44</v>
       </c>
       <c r="G95" s="10" t="n">
-        <v>0</v>
+        <v>1374797.36</v>
       </c>
       <c r="H95" s="11">
         <f>F95-G95</f>
@@ -4871,7 +4867,11 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K95" s="12" t="inlineStr"/>
+      <c r="K95" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 07.10.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 08.10.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4603,31 +4603,31 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>6024</v>
+        <v>9562</v>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>26  SOLAR Наземні СЕС Київ  шт. 0 шт. 0.77 Мвт SolarWind</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F90" s="10" t="n">
-        <v>246402</v>
+        <v>397353.6</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>0</v>
+        <v>397353.6</v>
       </c>
       <c r="H90" s="11">
         <f>F90-G90</f>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4647,14 +4647,14 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>6024</v>
+        <v>4766</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -4664,11 +4664,11 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>3999</v>
+        <v>1263447.42</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
@@ -4691,14 +4691,14 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>7244</v>
+        <v>6024</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
@@ -4708,11 +4708,11 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>132708.6</v>
+        <v>246402</v>
       </c>
       <c r="G92" s="10" t="n">
         <v>0</v>
@@ -4738,11 +4738,11 @@
         <v>46303</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>4766</v>
+        <v>6024</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>1263447.42</v>
+        <v>3999</v>
       </c>
       <c r="G93" s="10" t="n">
         <v>0</v>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4779,31 +4779,31 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>5910</v>
+        <v>7244</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>17297208.56</v>
+        <v>132708.6</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>16036852.56</v>
+        <v>0</v>
       </c>
       <c r="H94" s="11">
         <f>F94-G94</f>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4819,11 +4819,7 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K94" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
@@ -4844,14 +4840,14 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>2882721.44</v>
+        <v>17297208.56</v>
       </c>
       <c r="G95" s="10" t="n">
-        <v>1374797.36</v>
+        <v>16036852.56</v>
       </c>
       <c r="H95" s="11">
         <f>F95-G95</f>
@@ -4869,37 +4865,37 @@
       </c>
       <c r="K95" s="12" t="inlineStr">
         <is>
-          <t>€55 694</t>
+          <t>€334 181</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46309</v>
+        <v>46304</v>
       </c>
       <c r="B96" s="9" t="n">
-        <v>7414</v>
+        <v>5910</v>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>50822.46</v>
+        <v>2882721.44</v>
       </c>
       <c r="G96" s="10" t="n">
-        <v>0</v>
+        <v>1374797.36</v>
       </c>
       <c r="H96" s="11">
         <f>F96-G96</f>
@@ -4915,32 +4911,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K96" s="12" t="inlineStr"/>
+      <c r="K96" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B97" s="9" t="n">
-        <v>6352</v>
+        <v>7414</v>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>1119237.26</v>
+        <v>50822.46</v>
       </c>
       <c r="G97" s="10" t="n">
         <v>0</v>
@@ -4980,11 +4980,11 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>371982.96</v>
+        <v>1119237.26</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>0</v>
@@ -5007,28 +5007,28 @@
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B99" s="9" t="n">
-        <v>8497</v>
+        <v>6352</v>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>521482</v>
+        <v>371982.96</v>
       </c>
       <c r="G99" s="10" t="n">
         <v>0</v>
@@ -5047,27 +5047,23 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K99" s="12" t="inlineStr">
-        <is>
-          <t>€10 075</t>
-        </is>
-      </c>
+      <c r="K99" s="12" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46316</v>
+        <v>46311</v>
       </c>
       <c r="B100" s="9" t="n">
-        <v>6356</v>
+        <v>8497</v>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
@@ -5076,7 +5072,7 @@
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>3325062.4</v>
+        <v>521482</v>
       </c>
       <c r="G100" s="10" t="n">
         <v>0</v>
@@ -5097,34 +5093,34 @@
       </c>
       <c r="K100" s="12" t="inlineStr">
         <is>
-          <t>€64 240</t>
+          <t>€10 075</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>46321</v>
+        <v>46316</v>
       </c>
       <c r="B101" s="9" t="n">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F101" s="10" t="n">
-        <v>651792.28</v>
+        <v>3325062.4</v>
       </c>
       <c r="G101" s="10" t="n">
         <v>0</v>
@@ -5143,32 +5139,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K101" s="12" t="inlineStr"/>
+      <c r="K101" s="12" t="inlineStr">
+        <is>
+          <t>€64 240</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="B102" s="9" t="n">
-        <v>6356</v>
+        <v>6352</v>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F102" s="10" t="n">
-        <v>665012.48</v>
+        <v>651792.28</v>
       </c>
       <c r="G102" s="10" t="n">
         <v>0</v>
@@ -5187,36 +5187,32 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K102" s="12" t="inlineStr">
-        <is>
-          <t>€12 848</t>
-        </is>
-      </c>
+      <c r="K102" s="12" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B103" s="9" t="n">
-        <v>7894</v>
+        <v>6356</v>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F103" s="10" t="n">
-        <v>737597.4</v>
+        <v>665012.48</v>
       </c>
       <c r="G103" s="10" t="n">
         <v>0</v>
@@ -5235,32 +5231,36 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K103" s="12" t="inlineStr"/>
+      <c r="K103" s="12" t="inlineStr">
+        <is>
+          <t>€12 848</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>46330</v>
+        <v>46322</v>
       </c>
       <c r="B104" s="9" t="n">
-        <v>7508</v>
+        <v>7894</v>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F104" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>737597.4</v>
       </c>
       <c r="G104" s="10" t="n">
         <v>0</v>
@@ -5276,32 +5276,76 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="K104" s="12" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B105" s="9" t="n">
+        <v>7508</v>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="n">
+        <v>750999.9399999999</v>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="11">
+        <f>F105-G105</f>
+        <v/>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="K104" s="12" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="E105" s="3" t="inlineStr">
+      <c r="K105" s="12" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F105" s="13">
-        <f>SUM(F2:F104)</f>
-        <v/>
-      </c>
-      <c r="G105" s="13">
-        <f>SUM(G2:G104)</f>
-        <v/>
-      </c>
-      <c r="H105" s="13">
-        <f>SUM(H2:H104)</f>
+      <c r="F106" s="13">
+        <f>SUM(F2:F105)</f>
+        <v/>
+      </c>
+      <c r="G106" s="13">
+        <f>SUM(G2:G105)</f>
+        <v/>
+      </c>
+      <c r="H106" s="13">
+        <f>SUM(H2:H105)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I104"/>
+  <autoFilter ref="A1:I105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5567,7 +5611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5618,23 +5662,23 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>6024</v>
+        <v>4766</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>246402</v>
+        <v>1263447.42</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>0</v>
@@ -5646,23 +5690,23 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>7244</v>
+        <v>6024</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>132708.6</v>
+        <v>246402</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>0</v>
@@ -5674,26 +5718,26 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46260</v>
+        <v>46303</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>6406</v>
+        <v>7244</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>218602</v>
+        <v>132708.6</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -5702,26 +5746,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46301</v>
+        <v>46260</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>6024</v>
+        <v>6406</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>3999</v>
+        <v>218602</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -5729,26 +5773,54 @@
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="3" t="inlineStr">
+      <c r="A6" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>6024</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>3999</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11">
+        <f>E6-F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E6" s="13">
-        <f>SUM(E2:E5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="13">
-        <f>SUM(F2:F5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="13">
-        <f>SUM(G2:G5)</f>
+      <c r="E7" s="13">
+        <f>SUM(E2:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="13">
+        <f>SUM(F2:F6)</f>
+        <v/>
+      </c>
+      <c r="G7" s="13">
+        <f>SUM(G2:G6)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 08.10.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 30.10.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2588000</v>
+        <v>2525000</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2588000</v>
+        <v>2525000</v>
       </c>
       <c r="H10" s="11">
         <f>F10-G10</f>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>5176000</v>
+        <v>5050000</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>5176000</v>
+        <v>5050000</v>
       </c>
       <c r="H11" s="11">
         <f>F11-G11</f>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>2035935</v>
+        <v>2050102</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>2035935</v>
+        <v>2050102</v>
       </c>
       <c r="H15" s="11">
         <f>F15-G15</f>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="F39" s="10" t="n">
-        <v>1863360</v>
+        <v>1818000</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>1863360</v>
+        <v>1818000</v>
       </c>
       <c r="H39" s="11">
         <f>F39-G39</f>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="F44" s="10" t="n">
-        <v>455488</v>
+        <v>444400</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>455488</v>
+        <v>444400</v>
       </c>
       <c r="H44" s="11">
         <f>F44-G44</f>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="F54" s="10" t="n">
-        <v>8648578.4</v>
+        <v>8438045</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>8648578.4</v>
+        <v>8438045</v>
       </c>
       <c r="H54" s="11">
         <f>F54-G54</f>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="F57" s="10" t="n">
-        <v>4073512</v>
+        <v>3974350</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>4073512</v>
+        <v>3974350</v>
       </c>
       <c r="H57" s="11">
         <f>F57-G57</f>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="F66" s="10" t="n">
-        <v>4954726</v>
+        <v>4834112.5</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4954726</v>
+        <v>4834112.5</v>
       </c>
       <c r="H66" s="11">
         <f>F66-G66</f>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="F67" s="10" t="n">
-        <v>754402</v>
+        <v>736037.5</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>754402</v>
+        <v>736037.5</v>
       </c>
       <c r="H67" s="11">
         <f>F67-G67</f>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="F69" s="10" t="n">
-        <v>559784.4</v>
+        <v>546157.5</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>559784.4</v>
+        <v>546157.5</v>
       </c>
       <c r="H69" s="11">
         <f>F69-G69</f>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="F70" s="10" t="n">
-        <v>905800</v>
+        <v>883750</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>905800</v>
+        <v>883750</v>
       </c>
       <c r="H70" s="11">
         <f>F70-G70</f>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B71" s="9" t="n">
         <v>7414</v>
@@ -4084,10 +4084,10 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>2818642.56</v>
+        <v>2750028</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>2818642.56</v>
+        <v>2750028</v>
       </c>
       <c r="H78" s="11">
         <f>F78-G78</f>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1564446</v>
+        <v>1526362.5</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>1564446</v>
+        <v>1526362.5</v>
       </c>
       <c r="H80" s="11">
         <f>F80-G80</f>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="F87" s="10" t="n">
-        <v>574695</v>
+        <v>578694</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>574695</v>
+        <v>578694</v>
       </c>
       <c r="H87" s="11">
         <f>F87-G87</f>
@@ -4647,14 +4647,14 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>4766</v>
+        <v>6024</v>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
@@ -4664,14 +4664,14 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F91" s="10" t="n">
-        <v>1263447.42</v>
+        <v>246402</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>0</v>
+        <v>246402</v>
       </c>
       <c r="H91" s="11">
         <f>F91-G91</f>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4691,31 +4691,31 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>46303</v>
+        <v>46307</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>6024</v>
+        <v>8716</v>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>SOLAR Наземні СЕС Київ ТОВ ССДЖЕЙ УКРАЇНА</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F92" s="10" t="n">
-        <v>246402</v>
+        <v>1580000</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>0</v>
+        <v>1580000</v>
       </c>
       <c r="H92" s="11">
         <f>F92-G92</f>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4735,14 +4735,14 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>6024</v>
+        <v>7414</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
@@ -4752,14 +4752,14 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>3999</v>
+        <v>50823.44</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>0</v>
+        <v>50823.44</v>
       </c>
       <c r="H93" s="11">
         <f>F93-G93</f>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4779,14 +4779,14 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46303</v>
+        <v>46315</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>7244</v>
+        <v>6024</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>132708.6</v>
+        <v>3999</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>0</v>
+        <v>3999</v>
       </c>
       <c r="H94" s="11">
         <f>F94-G94</f>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4823,14 +4823,14 @@
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46304</v>
+        <v>46316</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>5910</v>
+        <v>6352</v>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -4840,14 +4840,14 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>17297208.56</v>
+        <v>1119237.26</v>
       </c>
       <c r="G95" s="10" t="n">
-        <v>16036852.56</v>
+        <v>1119237.26</v>
       </c>
       <c r="H95" s="11">
         <f>F95-G95</f>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4863,22 +4863,18 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K95" s="12" t="inlineStr">
-        <is>
-          <t>€334 181</t>
-        </is>
-      </c>
+      <c r="K95" s="12" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>46304</v>
+        <v>46316</v>
       </c>
       <c r="B96" s="9" t="n">
-        <v>5910</v>
+        <v>6352</v>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
@@ -4888,14 +4884,14 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>2882721.44</v>
+        <v>371982.96</v>
       </c>
       <c r="G96" s="10" t="n">
-        <v>1374797.36</v>
+        <v>371982.96</v>
       </c>
       <c r="H96" s="11">
         <f>F96-G96</f>
@@ -4903,7 +4899,7 @@
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -4911,39 +4907,35 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K96" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K96" s="12" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="B97" s="9" t="n">
-        <v>7414</v>
+        <v>6356</v>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>50822.46</v>
+        <v>3244120</v>
       </c>
       <c r="G97" s="10" t="n">
-        <v>0</v>
+        <v>3244120</v>
       </c>
       <c r="H97" s="11">
         <f>F97-G97</f>
@@ -4951,7 +4943,7 @@
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -4959,23 +4951,27 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K97" s="12" t="inlineStr"/>
+      <c r="K97" s="12" t="inlineStr">
+        <is>
+          <t>€64 240</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46310</v>
+        <v>46322</v>
       </c>
       <c r="B98" s="9" t="n">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -4984,10 +4980,10 @@
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>1119237.26</v>
+        <v>648824</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>0</v>
+        <v>648824</v>
       </c>
       <c r="H98" s="11">
         <f>F98-G98</f>
@@ -4995,7 +4991,7 @@
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5003,35 +4999,39 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K98" s="12" t="inlineStr"/>
+      <c r="K98" s="12" t="inlineStr">
+        <is>
+          <t>€12 848</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>46310</v>
+        <v>46325</v>
       </c>
       <c r="B99" s="9" t="n">
-        <v>6352</v>
+        <v>4766</v>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>371982.96</v>
+        <v>1263447.42</v>
       </c>
       <c r="G99" s="10" t="n">
-        <v>0</v>
+        <v>1050000</v>
       </c>
       <c r="H99" s="11">
         <f>F99-G99</f>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5051,31 +5051,31 @@
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46311</v>
+        <v>46325</v>
       </c>
       <c r="B100" s="9" t="n">
-        <v>8497</v>
+        <v>5910</v>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>521482</v>
+        <v>16876140.5</v>
       </c>
       <c r="G100" s="10" t="n">
-        <v>0</v>
+        <v>15646465.5</v>
       </c>
       <c r="H100" s="11">
         <f>F100-G100</f>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5093,37 +5093,37 @@
       </c>
       <c r="K100" s="12" t="inlineStr">
         <is>
-          <t>€10 075</t>
+          <t>€334 181</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>46316</v>
+        <v>46325</v>
       </c>
       <c r="B101" s="9" t="n">
-        <v>6356</v>
+        <v>5910</v>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F101" s="10" t="n">
-        <v>3325062.4</v>
+        <v>2812547</v>
       </c>
       <c r="G101" s="10" t="n">
-        <v>0</v>
+        <v>1341330.5</v>
       </c>
       <c r="H101" s="11">
         <f>F101-G101</f>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5141,25 +5141,25 @@
       </c>
       <c r="K101" s="12" t="inlineStr">
         <is>
-          <t>€64 240</t>
+          <t>€55 694</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>46321</v>
+        <v>46325</v>
       </c>
       <c r="B102" s="9" t="n">
-        <v>6352</v>
+        <v>7244</v>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="F102" s="10" t="n">
-        <v>651792.28</v>
+        <v>132708.6</v>
       </c>
       <c r="G102" s="10" t="n">
         <v>0</v>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>очікується</t>
+          <t>прострочено</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5191,28 +5191,28 @@
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
-        <v>46322</v>
+        <v>46332</v>
       </c>
       <c r="B103" s="9" t="n">
-        <v>6356</v>
+        <v>8497</v>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Іщук</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F103" s="10" t="n">
-        <v>665012.48</v>
+        <v>508787.5</v>
       </c>
       <c r="G103" s="10" t="n">
         <v>0</v>
@@ -5228,18 +5228,18 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="K103" s="12" t="inlineStr">
         <is>
-          <t>€12 848</t>
+          <t>€10 075</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>46322</v>
+        <v>46334</v>
       </c>
       <c r="B104" s="9" t="n">
         <v>7894</v>
@@ -5276,35 +5276,35 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="K104" s="12" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="n">
-        <v>46330</v>
+        <v>46342</v>
       </c>
       <c r="B105" s="9" t="n">
-        <v>7508</v>
+        <v>6352</v>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F105" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>651792.28</v>
       </c>
       <c r="G105" s="10" t="n">
         <v>0</v>
@@ -5326,26 +5326,114 @@
       <c r="K105" s="12" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="E106" s="3" t="inlineStr">
+      <c r="A106" s="8" t="n">
+        <v>46346</v>
+      </c>
+      <c r="B106" s="9" t="n">
+        <v>8716</v>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>SOLAR Наземні СЕС Київ ТОВ ССДЖЕЙ УКРАЇНА</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>Іщук</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>385933.6</v>
+      </c>
+      <c r="G106" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="11">
+        <f>F106-G106</f>
+        <v/>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="K106" s="12" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="n">
+        <v>46356</v>
+      </c>
+      <c r="B107" s="9" t="n">
+        <v>7508</v>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="n">
+        <v>750999.9399999999</v>
+      </c>
+      <c r="G107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="11">
+        <f>F107-G107</f>
+        <v/>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="K107" s="12" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F106" s="13">
-        <f>SUM(F2:F105)</f>
-        <v/>
-      </c>
-      <c r="G106" s="13">
-        <f>SUM(G2:G105)</f>
-        <v/>
-      </c>
-      <c r="H106" s="13">
-        <f>SUM(H2:H105)</f>
+      <c r="F108" s="13">
+        <f>SUM(F2:F107)</f>
+        <v/>
+      </c>
+      <c r="G108" s="13">
+        <f>SUM(G2:G107)</f>
+        <v/>
+      </c>
+      <c r="H108" s="13">
+        <f>SUM(H2:H107)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I105"/>
+  <autoFilter ref="A1:I107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5662,26 +5750,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46303</v>
+        <v>46325</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>4766</v>
+        <v>5910</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1263447.42</v>
+        <v>2812547</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>0</v>
+        <v>1341330.5</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -5690,26 +5778,26 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
-        <v>46303</v>
+        <v>46325</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>6024</v>
+        <v>5910</v>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="E3" s="11" t="n">
-        <v>246402</v>
+        <v>16876140.5</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>0</v>
+        <v>15646465.5</v>
       </c>
       <c r="G3" s="11">
         <f>E3-F3</f>
@@ -5718,14 +5806,14 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
-        <v>46303</v>
+        <v>46325</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>7244</v>
+        <v>4766</v>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -5734,10 +5822,10 @@
         </is>
       </c>
       <c r="E4" s="11" t="n">
-        <v>132708.6</v>
+        <v>1263447.42</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0</v>
+        <v>1050000</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
@@ -5746,26 +5834,26 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
-        <v>46260</v>
+        <v>46325</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>6406</v>
+        <v>7244</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Максим Яловий Чинадієво</t>
+          <t>В Модулекс модульна будівля Чернігів</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>218602</v>
+        <v>132708.6</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>170788</v>
+        <v>0</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
@@ -5774,26 +5862,26 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46303</v>
+        <v>46260</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>6024</v>
+        <v>6406</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3999</v>
+        <v>218602</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0</v>
+        <v>170788</v>
       </c>
       <c r="G6" s="11">
         <f>E6-F6</f>

--- a/pillar_cashflow.xlsx
+++ b/pillar_cashflow.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прострочені" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$107</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Графік надходжень'!$A$1:$I$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Прострочені'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Дані: 30.10.2026 · без проєктів на паузі/втрачених</t>
+          <t>Дані: 31.10.2026 · без проєктів на паузі/втрачених</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4735,31 +4735,31 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>7414</v>
+        <v>9698</v>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ Фундамент домобудування Володимир</t>
+          <t>26  ГШ Фундамент домобудування шт. 0 шт</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F93" s="10" t="n">
-        <v>50823.44</v>
+        <v>71830.08</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>50823.44</v>
+        <v>71830.08</v>
       </c>
       <c r="H93" s="11">
         <f>F93-G93</f>
@@ -4779,14 +4779,14 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>46315</v>
+        <v>46311</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>6024</v>
+        <v>7414</v>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
+          <t>-26 ГШ Фундамент домобудування Володимир</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3999</v>
+        <v>50823.44</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>3999</v>
+        <v>50823.44</v>
       </c>
       <c r="H94" s="11">
         <f>F94-G94</f>
@@ -4823,19 +4823,19 @@
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>6352</v>
+        <v>6024</v>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>-26 ГШ с. Липовиця Черніг. обл. Модулекс</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="F95" s="10" t="n">
-        <v>1119237.26</v>
+        <v>3999</v>
       </c>
       <c r="G95" s="10" t="n">
-        <v>1119237.26</v>
+        <v>3999</v>
       </c>
       <c r="H95" s="11">
         <f>F95-G95</f>
@@ -4870,28 +4870,24 @@
         <v>46316</v>
       </c>
       <c r="B96" s="9" t="n">
-        <v>6352</v>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>АБМК SCP Blade 8PS</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="C96" s="9" t="inlineStr"/>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Четвертий платіж</t>
+          <t>Авансовий платіж</t>
         </is>
       </c>
       <c r="F96" s="10" t="n">
-        <v>371982.96</v>
+        <v>139410</v>
       </c>
       <c r="G96" s="10" t="n">
-        <v>371982.96</v>
+        <v>139410</v>
       </c>
       <c r="H96" s="11">
         <f>F96-G96</f>
@@ -4914,28 +4910,28 @@
         <v>46316</v>
       </c>
       <c r="B97" s="9" t="n">
-        <v>6356</v>
+        <v>6352</v>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F97" s="10" t="n">
-        <v>3244120</v>
+        <v>1119237.26</v>
       </c>
       <c r="G97" s="10" t="n">
-        <v>3244120</v>
+        <v>1119237.26</v>
       </c>
       <c r="H97" s="11">
         <f>F97-G97</f>
@@ -4951,39 +4947,35 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K97" s="12" t="inlineStr">
-        <is>
-          <t>€64 240</t>
-        </is>
-      </c>
+      <c r="K97" s="12" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>46322</v>
+        <v>46316</v>
       </c>
       <c r="B98" s="9" t="n">
-        <v>6356</v>
+        <v>6352</v>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
+          <t>АБМК SCP Blade 8PS</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Хома</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Четвертий платіж</t>
         </is>
       </c>
       <c r="F98" s="10" t="n">
-        <v>648824</v>
+        <v>371982.96</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>648824</v>
+        <v>371982.96</v>
       </c>
       <c r="H98" s="11">
         <f>F98-G98</f>
@@ -4999,39 +4991,35 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K98" s="12" t="inlineStr">
-        <is>
-          <t>€12 848</t>
-        </is>
-      </c>
+      <c r="K98" s="12" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>46325</v>
+        <v>46316</v>
       </c>
       <c r="B99" s="9" t="n">
-        <v>4766</v>
+        <v>6356</v>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F99" s="10" t="n">
-        <v>1263447.42</v>
+        <v>3244120</v>
       </c>
       <c r="G99" s="10" t="n">
-        <v>1050000</v>
+        <v>3244120</v>
       </c>
       <c r="H99" s="11">
         <f>F99-G99</f>
@@ -5039,7 +5027,7 @@
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5047,35 +5035,39 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K99" s="12" t="inlineStr"/>
+      <c r="K99" s="12" t="inlineStr">
+        <is>
+          <t>€64 240</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>46325</v>
+        <v>46322</v>
       </c>
       <c r="B100" s="9" t="n">
-        <v>5910</v>
+        <v>6356</v>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>-26 SOLAR Наземні СЕС 3 Kirill Trokhin</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Хома</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж 60%</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F100" s="10" t="n">
-        <v>16876140.5</v>
+        <v>648824</v>
       </c>
       <c r="G100" s="10" t="n">
-        <v>15646465.5</v>
+        <v>648824</v>
       </c>
       <c r="H100" s="11">
         <f>F100-G100</f>
@@ -5083,7 +5075,7 @@
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5093,20 +5085,20 @@
       </c>
       <c r="K100" s="12" t="inlineStr">
         <is>
-          <t>€334 181</t>
+          <t>€12 848</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="B101" s="9" t="n">
-        <v>5910</v>
+        <v>9698</v>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>26  ГШ Фундамент домобудування шт. 0 шт</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
@@ -5116,14 +5108,14 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="F101" s="10" t="n">
-        <v>2812547</v>
+        <v>35830.08</v>
       </c>
       <c r="G101" s="10" t="n">
-        <v>1341330.5</v>
+        <v>35830.08</v>
       </c>
       <c r="H101" s="11">
         <f>F101-G101</f>
@@ -5131,7 +5123,7 @@
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>отримано</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5139,15 +5131,11 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="K101" s="12" t="inlineStr">
-        <is>
-          <t>€55 694</t>
-        </is>
-      </c>
+      <c r="K101" s="12" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>46325</v>
+        <v>46329</v>
       </c>
       <c r="B102" s="9" t="n">
         <v>7244</v>
@@ -5179,43 +5167,43 @@
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>прострочено</t>
+          <t>очікується</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="K102" s="12" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B103" s="9" t="n">
-        <v>8497</v>
+        <v>5910</v>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>LSG 110MWt   50 points</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Іщук</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>Другий платіж</t>
+          <t>Другий платіж 60%</t>
         </is>
       </c>
       <c r="F103" s="10" t="n">
-        <v>508787.5</v>
+        <v>16876140.5</v>
       </c>
       <c r="G103" s="10" t="n">
-        <v>0</v>
+        <v>15646465.5</v>
       </c>
       <c r="H103" s="11">
         <f>F103-G103</f>
@@ -5233,20 +5221,20 @@
       </c>
       <c r="K103" s="12" t="inlineStr">
         <is>
-          <t>€10 075</t>
+          <t>€334 181</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>46334</v>
+        <v>46331</v>
       </c>
       <c r="B104" s="9" t="n">
-        <v>7894</v>
+        <v>5910</v>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>SCP Фора  Хотів</t>
+          <t>SGM Brdovec, Хорватия</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
@@ -5256,14 +5244,14 @@
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>П'ятий платіж</t>
+          <t>Третій платіж</t>
         </is>
       </c>
       <c r="F104" s="10" t="n">
-        <v>737597.4</v>
+        <v>2812547</v>
       </c>
       <c r="G104" s="10" t="n">
-        <v>0</v>
+        <v>1341330.5</v>
       </c>
       <c r="H104" s="11">
         <f>F104-G104</f>
@@ -5279,23 +5267,27 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="K104" s="12" t="inlineStr"/>
+      <c r="K104" s="12" t="inlineStr">
+        <is>
+          <t>€55 694</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="n">
-        <v>46342</v>
+        <v>46332</v>
       </c>
       <c r="B105" s="9" t="n">
-        <v>6352</v>
+        <v>4766</v>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>АБМК SCP Blade 8PS</t>
+          <t>ALTECO Carport Model Taurus 280кВт</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Донська</t>
+          <t>Заянчковський</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
@@ -5304,10 +5296,10 @@
         </is>
       </c>
       <c r="F105" s="10" t="n">
-        <v>651792.28</v>
+        <v>1263447.42</v>
       </c>
       <c r="G105" s="10" t="n">
-        <v>0</v>
+        <v>1199397.83</v>
       </c>
       <c r="H105" s="11">
         <f>F105-G105</f>
@@ -5327,14 +5319,14 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>46346</v>
+        <v>46332</v>
       </c>
       <c r="B106" s="9" t="n">
-        <v>8716</v>
+        <v>8497</v>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>SOLAR Наземні СЕС Київ ТОВ ССДЖЕЙ УКРАЇНА</t>
+          <t>LSG 110MWt   50 points</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
@@ -5348,7 +5340,7 @@
         </is>
       </c>
       <c r="F106" s="10" t="n">
-        <v>385933.6</v>
+        <v>508787.5</v>
       </c>
       <c r="G106" s="10" t="n">
         <v>0</v>
@@ -5367,32 +5359,36 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="K106" s="12" t="inlineStr"/>
+      <c r="K106" s="12" t="inlineStr">
+        <is>
+          <t>€10 075</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="n">
-        <v>46356</v>
+        <v>46334</v>
       </c>
       <c r="B107" s="9" t="n">
-        <v>7508</v>
+        <v>7894</v>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>8602 Євген Весільна тераса Подорожнє</t>
+          <t>SCP Фора  Хотів</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Заянчковський</t>
+          <t>Донська</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>П'ятий платіж</t>
         </is>
       </c>
       <c r="F107" s="10" t="n">
-        <v>750999.9399999999</v>
+        <v>737597.4</v>
       </c>
       <c r="G107" s="10" t="n">
         <v>0</v>
@@ -5414,26 +5410,202 @@
       <c r="K107" s="12" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="E108" s="3" t="inlineStr">
+      <c r="A108" s="8" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B108" s="9" t="n">
+        <v>9698</v>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>26  ГШ Фундамент домобудування шт. 0 шт</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>35830.08</v>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="11">
+        <f>F108-G108</f>
+        <v/>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="K108" s="12" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="n">
+        <v>46342</v>
+      </c>
+      <c r="B109" s="9" t="n">
+        <v>6352</v>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>АБМК SCP Blade 8PS</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>Донська</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>П'ятий платіж</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="n">
+        <v>651792.28</v>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="11">
+        <f>F109-G109</f>
+        <v/>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="K109" s="12" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="n">
+        <v>46346</v>
+      </c>
+      <c r="B110" s="9" t="n">
+        <v>8716</v>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>SOLAR Наземні СЕС Київ ТОВ ССДЖЕЙ УКРАЇНА</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>Іщук</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>Другий платіж</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>385933.6</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="11">
+        <f>F110-G110</f>
+        <v/>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="K110" s="12" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="n">
+        <v>46356</v>
+      </c>
+      <c r="B111" s="9" t="n">
+        <v>7508</v>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>8602 Євген Весільна тераса Подорожнє</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>Заянчковський</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>Третій платіж</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="n">
+        <v>750999.9399999999</v>
+      </c>
+      <c r="G111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="11">
+        <f>F111-G111</f>
+        <v/>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>очікується</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="K111" s="12" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="F108" s="13">
-        <f>SUM(F2:F107)</f>
-        <v/>
-      </c>
-      <c r="G108" s="13">
-        <f>SUM(G2:G107)</f>
-        <v/>
-      </c>
-      <c r="H108" s="13">
-        <f>SUM(H2:H107)</f>
+      <c r="F112" s="13">
+        <f>SUM(F2:F111)</f>
+        <v/>
+      </c>
+      <c r="G112" s="13">
+        <f>SUM(G2:G111)</f>
+        <v/>
+      </c>
+      <c r="H112" s="13">
+        <f>SUM(H2:H111)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I107"/>
+  <autoFilter ref="A1:I111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5699,7 +5871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5750,26 +5922,26 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
-        <v>46325</v>
+        <v>46260</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>5910</v>
+        <v>6406</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>SGM Brdovec, Хорватия</t>
+          <t>Максим Яловий Чинадієво</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Третій платіж</t>
+          <t>Другий платіж</t>
         </is>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2812547</v>
+        <v>218602</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1341330.5</v>
+        <v>170788</v>
       </c>
       <c r="G2" s="11">
         <f>E2-F2</f>
@@ -5777,138 +5949,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
-        <v>46325</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>5910</v>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>SGM Brdovec, Хорватия</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж 60%</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>16876140.5</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>15646465.5</v>
-      </c>
-      <c r="G3" s="11">
-        <f>E3-F3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>46325</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>4766</v>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>ALTECO Carport Model Taurus 280кВт</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>П'ятий платіж</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>1263447.42</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="G4" s="11">
-        <f>E4-F4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>46325</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>7244</v>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>В Модулекс модульна будівля Чернігів</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>П'ятий платіж</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>132708.6</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="11">
-        <f>E5-F5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>6406</v>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Максим Яловий Чинадієво</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Другий платіж</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>218602</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>170788</v>
-      </c>
-      <c r="G6" s="11">
-        <f>E6-F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="E7" s="13">
-        <f>SUM(E2:E6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="13">
-        <f>SUM(F2:F6)</f>
-        <v/>
-      </c>
-      <c r="G7" s="13">
-        <f>SUM(G2:G6)</f>
+      <c r="E3" s="13">
+        <f>SUM(E2:E2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="13">
+        <f>SUM(F2:F2)</f>
+        <v/>
+      </c>
+      <c r="G3" s="13">
+        <f>SUM(G2:G2)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>